--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484664_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484664_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.3659</v>
+        <v>9.464</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0641</v>
+        <v>5.5833</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3018</v>
+        <v>3.8807</v>
       </c>
       <c r="G2" t="n">
         <v>1.4543</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9379</v>
+        <v>1.036</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5113</v>
+        <v>0.0306</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4266</v>
+        <v>1.0054</v>
       </c>
       <c r="V2" t="n">
         <v>5.691</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.448600000000001</v>
+        <v>7.932</v>
       </c>
       <c r="E3" t="n">
-        <v>9.0236</v>
+        <v>7.5812</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4251</v>
+        <v>0.3508</v>
       </c>
       <c r="G3" t="n">
         <v>7.0136</v>
@@ -688,13 +688,13 @@
         <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3864</v>
+        <v>0.8697</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2323</v>
+        <v>0.79</v>
       </c>
       <c r="U3" t="n">
-        <v>0.154</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0509</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2839</v>
+        <v>5.7021</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4259</v>
+        <v>3.522</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8581</v>
+        <v>2.1801</v>
       </c>
       <c r="G4" t="n">
         <v>2.18</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1589</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1637</v>
+        <v>0.2598</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0048</v>
+        <v>0.3173</v>
       </c>
       <c r="V4" t="n">
         <v>2.212</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6319</v>
+        <v>3.7658</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6959</v>
+        <v>3.1766</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>0.8051</v>
@@ -844,13 +844,13 @@
         <v>2.5656</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2848</v>
+        <v>-0.1508</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9909</v>
+        <v>-0.5102</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7062</v>
+        <v>0.3593</v>
       </c>
       <c r="V5" t="n">
         <v>1.4622</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.958</v>
+        <v>1.1285</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1908</v>
+        <v>0.287</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7672</v>
+        <v>0.8415</v>
       </c>
       <c r="G7" t="n">
         <v>0.6521</v>
@@ -1000,13 +1000,13 @@
         <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2438</v>
+        <v>-0.0733</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1652</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0043</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7855</v>
+        <v>-1.179</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.489</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2965</v>
+        <v>-0.5938</v>
       </c>
       <c r="G9" t="n">
         <v>1.6299</v>
@@ -1156,13 +1156,13 @@
         <v>2.3823</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2611</v>
+        <v>-0.1324</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1666</v>
+        <v>-0.2628</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4277</v>
+        <v>0.1304</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3937</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1462</v>
+        <v>-1.6571</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.283</v>
+        <v>0.3257</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1368</v>
+        <v>-1.9828</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.28</v>
+        <v>1.3439</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6369</v>
+        <v>1.2189</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9169</v>
+        <v>0.125</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4308</v>
+        <v>1.0252</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1333</v>
+        <v>0.291</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.5641</v>
+        <v>0.7342</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1508</v>
+        <v>0.3187</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5036</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3528</v>
+        <v>-0.6092</v>
       </c>
       <c r="P10" t="n">
         <v>-0.1833</v>
@@ -1234,28 +1234,28 @@
         <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>0.906</v>
+        <v>-0.2838</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0196</v>
+        <v>-0.1338</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9256</v>
+        <v>-0.1499</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5889</v>
+        <v>-2.5339</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5889</v>
+        <v>-3.8009</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1189</v>
+        <v>-1.6853</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0373</v>
+        <v>-2.4753</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1562</v>
+        <v>0.79</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3439</v>
+        <v>-0.28</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2189</v>
+        <v>2.6369</v>
       </c>
       <c r="I11" t="n">
-        <v>0.125</v>
+        <v>-2.9169</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0252</v>
+        <v>-0.4308</v>
       </c>
       <c r="K11" t="n">
-        <v>0.291</v>
+        <v>2.1333</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7342</v>
+        <v>-2.5641</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3187</v>
+        <v>0.1508</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.5036</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6092</v>
+        <v>-0.3528</v>
       </c>
       <c r="P11" t="n">
         <v>-0.1833</v>
@@ -1312,22 +1312,22 @@
         <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7456</v>
+        <v>0.3669</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4223</v>
+        <v>-0.2119</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3233</v>
+        <v>0.5788</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.5339</v>
+        <v>-1.5889</v>
       </c>
       <c r="W11" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.8009</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2363</v>
+        <v>-3.3591</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5229</v>
+        <v>-3.0421</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7134</v>
+        <v>-0.317</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1612</v>
@@ -1390,13 +1390,13 @@
         <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0925</v>
+        <v>-0.2153</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6976</v>
+        <v>-0.2168</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3949</v>
+        <v>0.0015</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7156</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0423</v>
+        <v>-5.5804</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.0751</v>
+        <v>-5.7866</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0328</v>
+        <v>0.2062</v>
       </c>
       <c r="G13" t="n">
         <v>-2.068</v>
@@ -1468,13 +1468,13 @@
         <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1149</v>
+        <v>0.5767</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1297</v>
+        <v>0.1588</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2446</v>
+        <v>0.418</v>
       </c>
       <c r="V13" t="n">
         <v>-1.89</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.962300000000001</v>
+        <v>-9.1347</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.048</v>
+        <v>-6.5672</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9143</v>
+        <v>-2.5675</v>
       </c>
       <c r="G14" t="n">
         <v>-2.8957</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2906</v>
+        <v>-0.463</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8808</v>
+        <v>-0.4001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4098</v>
+        <v>-0.063</v>
       </c>
       <c r="V14" t="n">
         <v>-2.6606</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.597700000000001</v>
+        <v>8.597699999999998</v>
       </c>
       <c r="E15" t="n">
-        <v>5.220499999999996</v>
+        <v>5.220299999999998</v>
       </c>
       <c r="F15" t="n">
-        <v>3.377399999999999</v>
+        <v>3.3774</v>
       </c>
       <c r="G15" t="n">
         <v>10.8749</v>
@@ -1603,10 +1603,10 @@
         <v>14.4707</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9637999999999995</v>
+        <v>0.9638</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.559800000000001</v>
+        <v>-4.559799999999999</v>
       </c>
       <c r="N15" t="n">
         <v>1.693</v>
@@ -1624,10 +1624,10 @@
         <v>19.242</v>
       </c>
       <c r="S15" t="n">
-        <v>2.107899999999999</v>
+        <v>2.107799999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5654</v>
+        <v>-0.5653999999999999</v>
       </c>
       <c r="U15" t="n">
         <v>2.6732</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9675</v>
+        <v>6.6638</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2449</v>
+        <v>5.1103</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7226</v>
+        <v>1.5536</v>
       </c>
       <c r="G16" t="n">
         <v>0.8504</v>
@@ -1702,13 +1702,13 @@
         <v>3.6651</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5451</v>
+        <v>0.1512</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3763</v>
+        <v>-0.5109</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8312</v>
+        <v>0.6621</v>
       </c>
       <c r="V16" t="n">
         <v>4.7459</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8613</v>
+        <v>1.224</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.219</v>
+        <v>0.0694</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0803</v>
+        <v>1.1546</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1596</v>
@@ -1858,13 +1858,13 @@
         <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8117</v>
+        <v>-0.4489</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.4823</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.041</v>
+        <v>0.0334</v>
       </c>
       <c r="V18" t="n">
         <v>0.6335</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.473</v>
+        <v>0.6289</v>
       </c>
       <c r="E19" t="n">
-        <v>4.0515</v>
+        <v>3.9554</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5785</v>
+        <v>-3.3265</v>
       </c>
       <c r="G19" t="n">
         <v>2.2651</v>
@@ -1936,13 +1936,13 @@
         <v>0.3665</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2477</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0355</v>
+        <v>-0.0607</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2832</v>
+        <v>-0.0311</v>
       </c>
       <c r="V19" t="n">
         <v>-1.9109</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0298</v>
+        <v>0.3082</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9764</v>
+        <v>-0.6879</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9466</v>
+        <v>0.9961</v>
       </c>
       <c r="G20" t="n">
         <v>0.8875</v>
@@ -2014,13 +2014,13 @@
         <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8282</v>
+        <v>-0.4902</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.046</v>
+        <v>-0.7575</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2178</v>
+        <v>0.2673</v>
       </c>
       <c r="V20" t="n">
         <v>0.6439</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0314</v>
+        <v>-0.1713</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9459</v>
+        <v>-2.2344</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9145</v>
+        <v>2.0631</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3968</v>
@@ -2092,13 +2092,13 @@
         <v>2.3823</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4649</v>
+        <v>0.325</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4563</v>
+        <v>0.1678</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0086</v>
+        <v>0.1572</v>
       </c>
       <c r="V21" t="n">
         <v>1.267</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4499</v>
+        <v>-0.7953</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2515</v>
+        <v>-0.1554</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1984</v>
+        <v>-0.64</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9228</v>
@@ -2170,13 +2170,13 @@
         <v>3.2986</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0801</v>
+        <v>-0.2653</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7353</v>
+        <v>-0.6391</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8154</v>
+        <v>0.3738</v>
       </c>
       <c r="V22" t="n">
         <v>0.0104</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.367</v>
+        <v>-0.8119</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.4613</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4249</v>
+        <v>-0.3506</v>
       </c>
       <c r="G23" t="n">
         <v>0.9394</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0681</v>
+        <v>-0.513</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.29</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2974</v>
+        <v>-0.2231</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3219</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. GARCIA JIMENEZ</t>
+          <t>B. KABASELE KATUMBA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7791</v>
+        <v>-1.6874</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4654</v>
+        <v>0.2794</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6863</v>
+        <v>-1.9669</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5584</v>
+        <v>-0.7524</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1545</v>
+        <v>-1.3581</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5962</v>
+        <v>0.6057</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1554</v>
+        <v>-0.0516</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2387</v>
+        <v>-0.1767</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0833</v>
+        <v>0.125</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.403</v>
+        <v>-0.7008</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-1.1815</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5128</v>
+        <v>0.4807</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R24" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5569</v>
+        <v>0.3528</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2006</v>
+        <v>-0.0196</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3562</v>
+        <v>0.3723</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3219</v>
+        <v>-1.2878</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-2.5548</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B. KABASELE KATUMBA</t>
+          <t>L. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8113</v>
+        <v>-2.2628</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2794</v>
+        <v>-2.85</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0908</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7524</v>
+        <v>-1.5584</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.3581</v>
+        <v>-2.1545</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6057</v>
+        <v>0.5962</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0516</v>
+        <v>-1.1554</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1767</v>
+        <v>-1.2387</v>
       </c>
       <c r="L25" t="n">
-        <v>0.125</v>
+        <v>0.0833</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7008</v>
+        <v>-0.403</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.1815</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>0.4807</v>
+        <v>0.5128</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2289</v>
+        <v>0.0732</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0196</v>
+        <v>-0.184</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2485</v>
+        <v>0.2572</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2878</v>
+        <v>0.3219</v>
       </c>
       <c r="W25" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.5548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.182</v>
+        <v>-5.718</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0261</v>
+        <v>-2.9877</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.1558</v>
+        <v>-2.7304</v>
       </c>
       <c r="G26" t="n">
         <v>-5.1848</v>
@@ -2482,13 +2482,13 @@
         <v>2.0158</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4531</v>
+        <v>-0.083</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1524</v>
+        <v>0.1908</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6993</v>
+        <v>-0.2738</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6335</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.8245</v>
+        <v>-6.9104</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.7022</v>
+        <v>-4.9907</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.1223</v>
+        <v>-1.9197</v>
       </c>
       <c r="G27" t="n">
         <v>-4.4178</v>
@@ -2560,13 +2560,13 @@
         <v>0.733</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.3909</v>
+        <v>-0.4768</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2006</v>
+        <v>-0.0878</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.5915</v>
+        <v>-0.389</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-8.597900000000001</v>
+        <v>-7.9569</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.377400000000001</v>
+        <v>-3.377600000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.2204</v>
+        <v>-4.5795</v>
       </c>
       <c r="G28" t="n">
         <v>-10.8749</v>
@@ -2638,13 +2638,13 @@
         <v>20.1581</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.1078</v>
+        <v>-1.4668</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.6732</v>
+        <v>-2.673300000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>0.5653</v>
+        <v>1.2063</v>
       </c>
       <c r="V28" t="n">
         <v>3.468500000000001</v>
